--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-27).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-27).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>20</t>
+    <t>17</t>
   </si>
   <si>
-    <t>R$ 4.370,01</t>
+    <t>R$ 4.349,10</t>
   </si>
   <si>
-    <t>47.4</t>
+    <t>47.2</t>
   </si>
   <si>
     <t>29.5</t>
   </si>
   <si>
-    <t>4.68</t>
+    <t>4.69</t>
   </si>
   <si>
-    <t>17.7</t>
+    <t>17.8</t>
   </si>
   <si>
-    <t>6.8</t>
+    <t>6.9</t>
   </si>
   <si>
     <t>6.5</t>
   </si>
   <si>
-    <t>45.7%</t>
+    <t>46.0%</t>
   </si>
   <si>
     <t>21.6%</t>
@@ -6855,7 +6855,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6885,14 +6885,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>3749.8800000000001</v>
+      </c>
+      <c r="N36" s="6">
+        <v>51</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>5.8785249999999998</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>24.922082499999998</v>
+      </c>
+      <c r="R36" s="8">
+        <v>12.030769230769231</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.375</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9144,7 +9156,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9174,14 +9186,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>533.39999999999998</v>
+      </c>
+      <c r="N51" s="6">
+        <v>5</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>4.96</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>19.344433333333331</v>
+      </c>
+      <c r="R51" s="8">
+        <v>8.8389000000000006</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14846,7 +14870,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14874,14 +14898,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>4707.7799999999997</v>
+      </c>
+      <c r="N89" s="6">
+        <v>50</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>5.0135416666666668</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>20.985714285714284</v>
+      </c>
+      <c r="R89" s="8">
+        <v>7.6142857142857148</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.14285714285714285</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
